--- a/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="域变更日志" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B13" s="42" t="inlineStr">
         <is>
-          <t>关卡选择</t>
+          <t>远征全息城市选关</t>
         </is>
       </c>
       <c r="C13" s="54" t="inlineStr">
@@ -2649,46 +2649,54 @@
       <c r="G13" s="54" t="n"/>
       <c r="H13" s="42" t="inlineStr">
         <is>
-          <t>屏幕空间</t>
+          <t>世界空间3D近景</t>
         </is>
       </c>
       <c r="I13" s="54" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>主楼先起/双入口错峰/波浪扫描/方块粒子/倒序收起</t>
         </is>
       </c>
       <c r="J13" s="42" t="inlineStr">
         <is>
-          <t>跨分辨率</t>
+          <t>99F中央全息平台</t>
         </is>
       </c>
       <c r="K13" s="42" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>原型已接入</t>
         </is>
       </c>
       <c r="L13" s="54" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="M13" s="54" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v002</t>
         </is>
       </c>
       <c r="N13" s="54" t="inlineStr">
         <is>
-          <t>1280×720 基准；九宫格/矢量优先</t>
-        </is>
-      </c>
-      <c r="O13" s="54" t="n"/>
+          <t>主体约3.1m宽；42座外缘错落楼群；径向密度衰减；GPU逐块升降；2座楼顶入口</t>
+        </is>
+      </c>
+      <c r="O13" s="54" t="inlineStr">
+        <is>
+          <t>assets/art/ui/expedition_city/hologram_city.tscn</t>
+        </is>
+      </c>
       <c r="P13" s="54" t="inlineStr">
         <is>
-          <t>src/ui/LevelSelectMenu.gd</t>
-        </is>
-      </c>
-      <c r="Q13" s="54" t="n"/>
+          <t>scenes/RogueMapSelectMenu.gd; src/ui/HologramCity3D.gd; docs/v0.1/design/远征全息城市交互设计.md</t>
+        </is>
+      </c>
+      <c r="Q13" s="54" t="inlineStr">
+        <is>
+          <t>远征情报室;全息城市;镜头拉近;远征01;测试99;3D选关</t>
+        </is>
+      </c>
       <c r="R13" s="54">
         <f>LOWER(TRIM(C13)&amp;"|"&amp;TRIM(D13)&amp;"|"&amp;TRIM(E13)&amp;"|"&amp;TRIM(F13)&amp;"|"&amp;TRIM(H13)&amp;"|"&amp;TRIM(I13))</f>
         <v/>
@@ -2697,18 +2705,22 @@
         <f>IF(COUNTIF($R$6:$R$21,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T13" s="54" t="n"/>
+      <c r="T13" s="54" t="inlineStr">
+        <is>
+          <t>bcecf005d4052b9f701ae6c88fc659aeaf796dcb519f3ac8cdfe9e37d9d8357f</t>
+        </is>
+      </c>
       <c r="U13" s="42" t="inlineStr">
         <is>
-          <t>待分配</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="V13" s="55" t="n">
-        <v>46224</v>
+        <v>46294</v>
       </c>
       <c r="W13" s="42" t="inlineStr">
         <is>
-          <t>原创/待确认</t>
+          <t>项目原创程序几何；用户提供风格参考</t>
         </is>
       </c>
       <c r="X13" s="53" t="inlineStr">
@@ -2718,7 +2730,7 @@
       </c>
       <c r="Y13" s="42" t="inlineStr">
         <is>
-          <t>先建组件库，再做页面，避免每页重复画按钮/面板</t>
+          <t>2026-09-29：按用户参考制作Box城市；提前1秒展开，继承原环境至近景后渐暗；主楼优先/入口错峰/方块过渡；同场景世界空间入口。真实渲染/点击/键盘/手柄/返程通过，参考图像素级一致性未签署。</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="29" min="1" max="1"/>
@@ -5348,6 +5360,43 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>v0.2.1</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>选关表现替换</t>
+        </is>
+      </c>
+      <c r="D7" s="40" t="inlineStr">
+        <is>
+          <t>UI-SCREEN-LEVEL-SELECT</t>
+        </is>
+      </c>
+      <c r="E7" s="41" t="inlineStr">
+        <is>
+          <t>原弹窗改为平台锚定全息城市及专属镜头</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>ID与出发携带物契约保持</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
@@ -12,7 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$22</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
@@ -1066,22 +1068,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="30">
       <c r="A6" s="35">
-        <f>COUNTA('资产主表'!$A$6:$A$21)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$22)</f>
         <v/>
       </c>
       <c r="B6" s="33" t="n"/>
       <c r="C6" s="35">
-        <f>COUNTIF('资产主表'!$K$6:$K$21,"已完成")+COUNTIF('资产主表'!$K$6:$K$21,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$21,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$21,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$21,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$21,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$21,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$22,"已完成")+COUNTIF('资产主表'!$K$6:$K$22,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$22,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$22,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$22,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$22,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$22,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="35">
-        <f>COUNTIF('资产主表'!$K$6:$K$21,"待制作")+COUNTIF('资产主表'!$K$6:$K$21,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$22,"待制作")+COUNTIF('资产主表'!$K$6:$K$22,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="33" t="n"/>
       <c r="G6" s="35">
-        <f>COUNTIF('资产主表'!$S$6:$S$21,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$22,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="33" t="n"/>
@@ -1150,11 +1152,11 @@
         </is>
       </c>
       <c r="B10" s="40">
-        <f>COUNTIF('资产主表'!$C$6:$C$21,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$22,A10)</f>
         <v/>
       </c>
       <c r="C10" s="40">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$21=A10)*(('资产主表'!$K$6:$K$21="已完成")+('资产主表'!$K$6:$K$21="原型已接入")+('资产主表'!$K$6:$K$21="正式美术已接入")+('资产主表'!$K$6:$K$21="已优化并正式接入")+('资产主表'!$K$6:$K$21="Blender源已完成")+('资产主表'!$K$6:$K$21="已导入；优化完成")+('资产主表'!$K$6:$K$21="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$22=A10)*(('资产主表'!$K$6:$K$22="已完成")+('资产主表'!$K$6:$K$22="原型已接入")+('资产主表'!$K$6:$K$22="正式美术已接入")+('资产主表'!$K$6:$K$22="已优化并正式接入")+('资产主表'!$K$6:$K$22="Blender源已完成")+('资产主表'!$K$6:$K$22="已导入；优化完成")+('资产主表'!$K$6:$K$22="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="40" t="n"/>
@@ -1172,11 +1174,11 @@
         </is>
       </c>
       <c r="B11" s="40">
-        <f>COUNTIF('资产主表'!$C$6:$C$21,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$22,A11)</f>
         <v/>
       </c>
       <c r="C11" s="40">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$21=A11)*(('资产主表'!$K$6:$K$21="已完成")+('资产主表'!$K$6:$K$21="原型已接入")+('资产主表'!$K$6:$K$21="正式美术已接入")+('资产主表'!$K$6:$K$21="已优化并正式接入")+('资产主表'!$K$6:$K$21="Blender源已完成")+('资产主表'!$K$6:$K$21="已导入；优化完成")+('资产主表'!$K$6:$K$21="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$22=A11)*(('资产主表'!$K$6:$K$22="已完成")+('资产主表'!$K$6:$K$22="原型已接入")+('资产主表'!$K$6:$K$22="正式美术已接入")+('资产主表'!$K$6:$K$22="已优化并正式接入")+('资产主表'!$K$6:$K$22="Blender源已完成")+('资产主表'!$K$6:$K$22="已导入；优化完成")+('资产主表'!$K$6:$K$22="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="40" t="n"/>
@@ -1939,7 +1941,7 @@
         <v/>
       </c>
       <c r="S6" s="51">
-        <f>IF(COUNTIF($R$6:$R$21,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="50" t="inlineStr">
@@ -2052,7 +2054,7 @@
         <v/>
       </c>
       <c r="S7" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="54" t="n"/>
@@ -2159,7 +2161,7 @@
         <v/>
       </c>
       <c r="S8" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="54" t="n"/>
@@ -2266,7 +2268,7 @@
         <v/>
       </c>
       <c r="S9" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="54" t="n"/>
@@ -2373,7 +2375,7 @@
         <v/>
       </c>
       <c r="S10" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="54" t="n"/>
@@ -2480,7 +2482,7 @@
         <v/>
       </c>
       <c r="S11" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="54" t="n"/>
@@ -2587,7 +2589,7 @@
         <v/>
       </c>
       <c r="S12" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="54" t="n"/>
@@ -2702,7 +2704,7 @@
         <v/>
       </c>
       <c r="S13" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="54" t="inlineStr">
@@ -2813,7 +2815,7 @@
         <v/>
       </c>
       <c r="S14" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="54" t="n"/>
@@ -2920,7 +2922,7 @@
         <v/>
       </c>
       <c r="S15" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="54" t="n"/>
@@ -3027,7 +3029,7 @@
         <v/>
       </c>
       <c r="S16" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="54" t="n"/>
@@ -3134,7 +3136,7 @@
         <v/>
       </c>
       <c r="S17" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="54" t="n"/>
@@ -3253,7 +3255,7 @@
         <v/>
       </c>
       <c r="S18" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="54" t="inlineStr">
@@ -3373,7 +3375,7 @@
         <v/>
       </c>
       <c r="S19" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="54" t="inlineStr">
@@ -3497,7 +3499,7 @@
         <v/>
       </c>
       <c r="S20" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="54" t="inlineStr">
@@ -3620,7 +3622,7 @@
         <v/>
       </c>
       <c r="S21" s="42">
-        <f>IF(COUNTIF($R$6:$R$21,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$22,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="54" t="inlineStr">
@@ -3654,32 +3656,128 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="30">
-      <c r="A22" s="54" t="n"/>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="54" t="n"/>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="54" t="n"/>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="54" t="n"/>
-      <c r="K22" s="42" t="n"/>
-      <c r="L22" s="54" t="n"/>
-      <c r="M22" s="54" t="n"/>
-      <c r="N22" s="54" t="n"/>
-      <c r="O22" s="54" t="n"/>
-      <c r="P22" s="54" t="n"/>
-      <c r="Q22" s="54" t="n"/>
-      <c r="R22" s="54" t="n"/>
-      <c r="S22" s="42" t="n"/>
-      <c r="T22" s="54" t="n"/>
-      <c r="U22" s="54" t="n"/>
-      <c r="V22" s="55" t="n"/>
-      <c r="W22" s="54" t="n"/>
-      <c r="X22" s="53" t="n"/>
-      <c r="Y22" s="54" t="n"/>
+    <row r="22" ht="126.85" customHeight="1" s="30">
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>UI-ATLAS-FATE-CARD</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>命运塔罗卡面集</t>
+        </is>
+      </c>
+      <c r="C22" s="54" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>atlas</t>
+        </is>
+      </c>
+      <c r="E22" s="54" t="inlineStr">
+        <is>
+          <t>fate_card_atlas</t>
+        </is>
+      </c>
+      <c r="F22" s="54" t="inlineStr">
+        <is>
+          <t>card</t>
+        </is>
+      </c>
+      <c r="G22" s="54" t="inlineStr">
+        <is>
+          <t>UI-SCREEN-FATE-SELECT</t>
+        </is>
+      </c>
+      <c r="H22" s="42" t="inlineStr">
+        <is>
+          <t>2D卡片贴图</t>
+        </is>
+      </c>
+      <c r="I22" s="54" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J22" s="42" t="inlineStr">
+        <is>
+          <t>命运卡三选一/占卜屋/工作台/命运卡收藏室</t>
+        </is>
+      </c>
+      <c r="K22" s="42" t="inlineStr">
+        <is>
+          <t>原型已接入</t>
+        </is>
+      </c>
+      <c r="L22" s="54" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="M22" s="54" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N22" s="54" t="inlineStr">
+        <is>
+          <t>卡面宽683×高1024 RGBA透明（统一高1024、紧贴卡片本体）；卡背1369×2048成品(含圆角)</t>
+        </is>
+      </c>
+      <c r="O22" s="54" t="inlineStr">
+        <is>
+          <t>assets/art/ui/fate_cards/ui_fate_card_back_v001.png;assets/art/ui/fate_cards/ui_fate_card_armor_pierce_v001.png;assets/art/ui/fate_cards/ui_fate_card_attachment_parasite_v001.png;assets/art/ui/fate_cards/ui_fate_card_barrage_copy_v001.png;assets/art/ui/fate_cards/ui_fate_card_bless_dead_v001.png;assets/art/ui/fate_cards/ui_fate_card_bounce_bullet_v001.png;assets/art/ui/fate_cards/ui_fate_card_bullet_carry_gun_v001.png;assets/art/ui/fate_cards/ui_fate_card_bullet_return_v001.png;assets/art/ui/fate_cards/ui_fate_card_chain_lightning_v001.png;assets/art/ui/fate_cards/ui_fate_card_crit_kill_v001.png;assets/art/ui/fate_cards/ui_fate_card_curse_map_v001.png;assets/art/ui/fate_cards/ui_fate_card_every_seventh_v001.png;assets/art/ui/fate_cards/ui_fate_card_explode_reload_v001.png;assets/art/ui/fate_cards/ui_fate_card_extra_loot_v001.png;assets/art/ui/fate_cards/ui_fate_card_fuse_fire_v001.png;assets/art/ui/fate_cards/ui_fate_card_fuse_frost_v001.png;assets/art/ui/fate_cards/ui_fate_card_fuse_poison_v001.png;assets/art/ui/fate_cards/ui_fate_card_gluttony_v001.png;assets/art/ui/fate_cards/ui_fate_card_gun_on_gun_v001.png;assets/art/ui/fate_cards/ui_fate_card_home_on_land_v001.png;assets/art/ui/fate_cards/ui_fate_card_huge_scale_v001.png;assets/art/ui/fate_cards/ui_fate_card_living_bullet_v001.png;assets/art/ui/fate_cards/ui_fate_card_lucky_chest_v001.png;assets/art/ui/fate_cards/ui_fate_card_mark_enemy_v001.png;assets/art/ui/fate_cards/ui_fate_card_moon_ammo_v001.png;assets/art/ui/fate_cards/ui_fate_card_moon_dash_v001.png;assets/art/ui/fate_cards/ui_fate_card_moon_elite_heal_v001.png;assets/art/ui/fate_cards/ui_fate_card_moon_first_hit_v001.png;assets/art/ui/fate_cards/ui_fate_card_moon_guard_v001.png;assets/art/ui/fate_cards/ui_fate_card_moon_last_stand_v001.png;assets/art/ui/fate_cards/ui_fate_card_moon_power_v001.png;assets/art/ui/fate_cards/ui_fate_card_moon_room_heal_v001.png;assets/art/ui/fate_cards/ui_fate_card_moon_stride_v001.png;assets/art/ui/fate_cards/ui_fate_card_moon_vitality_v001.png;assets/art/ui/fate_cards/ui_fate_card_out_of_control_v001.png;assets/art/ui/fate_cards/ui_fate_card_overclock_v001.png;assets/art/ui/fate_cards/ui_fate_card_reinforce_v001.png;assets/art/ui/fate_cards/ui_fate_card_scale_node_v001.png;assets/art/ui/fate_cards/ui_fate_card_sun_bounty_v001.png;assets/art/ui/fate_cards/ui_fate_card_sun_currency_v001.png;assets/art/ui/fate_cards/ui_fate_card_sun_extra_loot_v001.png;assets/art/ui/fate_cards/ui_fate_card_sun_extraction_v001.png;assets/art/ui/fate_cards/ui_fate_card_sun_key_v001.png;assets/art/ui/fate_cards/ui_fate_card_sun_quality_v001.png;assets/art/ui/fate_cards/ui_fate_card_sun_reinforce_v001.png;assets/art/ui/fate_cards/ui_fate_card_sun_reveal_v001.png;assets/art/ui/fate_cards/ui_fate_card_sun_scorch_v001.png;assets/art/ui/fate_cards/ui_fate_card_sun_trial_v001.png;assets/art/ui/fate_cards/ui_fate_card_turret_on_land_v001.png</t>
+        </is>
+      </c>
+      <c r="P22" s="54" t="inlineStr">
+        <is>
+          <t>src/weapons/FateCardView.gd;src/world3d/Dungeon3D.gd;src/ui/DivinationMenu.gd;src/ui/WorkbenchPanel.gd;src/ui/FateCardCollectionMenu.gd</t>
+        </is>
+      </c>
+      <c r="Q22" s="54" t="inlineStr">
+        <is>
+          <t>塔罗;命运卡;卡面;卡背;塔罗牌;fate card;tarot;霓虹绿;兔子机器人</t>
+        </is>
+      </c>
+      <c r="R22" s="54">
+        <f>LOWER(TRIM(C22)&amp;"|"&amp;TRIM(D22)&amp;"|"&amp;TRIM(E22)&amp;"|"&amp;TRIM(F22)&amp;"|"&amp;TRIM(H22)&amp;"|"&amp;TRIM(I22))</f>
+        <v/>
+      </c>
+      <c r="S22" s="42">
+        <f>IF(COUNTIF($R$6:$R$22,R22)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T22" s="54" t="inlineStr">
+        <is>
+          <t>25d539baf0235253fbd960a1d1d27ac79e3b53fbaaf6dfce8ef4207290c185ed</t>
+        </is>
+      </c>
+      <c r="U22" s="54" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V22" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="W22" s="42" t="inlineStr">
+        <is>
+          <t>用户提供塔罗牌阵图拆分 + 原创AI补图</t>
+        </is>
+      </c>
+      <c r="X22" s="53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y22" s="42" t="inlineStr">
+        <is>
+          <t>命运卡由程序绘制改为塔罗图卡呈现，48张可玩卡全量覆盖。卡面按 stable_card_id 命名；缺图的卡由 FateCardView.art_for() 返回 null 并回退程序卡面（本行已无缺图，回退路径保留为容错）。逆位只倒置卡面图案，卡下功能文字保持正向；卡背全卡共用。30张取自用户塔罗牌阵拆分图，18张按同风格补生成并做绿色归一化+线条加粗对齐既有卡面。</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="30">
       <c r="A23" s="54" t="n"/>
@@ -5209,6 +5307,7 @@
     <row r="427" ht="84.75" customHeight="1" s="30"/>
     <row r="429" ht="120" customHeight="1" s="30"/>
   </sheetData>
+  <autoFilter ref="A5:X22"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -5227,19 +5326,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="C23:C79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="C23:C79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K6:K79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="K6:K79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L6:L79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="L6:L79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="C6:C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="C6:C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"UI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5259,7 +5358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="29" min="1" max="1"/>
@@ -5397,6 +5496,80 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t>v0.2.2</t>
+        </is>
+      </c>
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>表现替换</t>
+        </is>
+      </c>
+      <c r="D8" s="40" t="inlineStr">
+        <is>
+          <t>UI-ATLAS-FATE-CARD</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="inlineStr">
+        <is>
+          <t>命运塔罗卡面接入：命运卡由程序绘制改为塔罗图卡呈现，新增卡面集（1卡背+30卡面，按 stable_card_id 命名）；缺图卡回退程序卡面。功能与抽卡逻辑不变。</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>仅表现层变更；AssetID/存档/卡牌定义与数值不受影响。</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>v0.2.3</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>补图完成</t>
+        </is>
+      </c>
+      <c r="D9" s="40" t="inlineStr">
+        <is>
+          <t>UI-ATLAS-FATE-CARD</t>
+        </is>
+      </c>
+      <c r="E9" s="41" t="inlineStr">
+        <is>
+          <t>命运塔罗卡面补全：新增18张按同风格生成的牌面，48张可玩卡全量覆盖，缺图回退路径保留为容错。</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>仅表现层变更；AssetID/存档/卡牌定义与数值不受影响。</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -1068,22 +1068,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="30">
       <c r="A6" s="35">
-        <f>COUNTA('资产主表'!$A$6:$A$22)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$23)</f>
         <v/>
       </c>
       <c r="B6" s="33" t="n"/>
       <c r="C6" s="35">
-        <f>COUNTIF('资产主表'!$K$6:$K$22,"已完成")+COUNTIF('资产主表'!$K$6:$K$22,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$22,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$22,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$22,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$22,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$22,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$23,"已完成")+COUNTIF('资产主表'!$K$6:$K$23,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$23,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$23,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$23,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$23,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$23,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="35">
-        <f>COUNTIF('资产主表'!$K$6:$K$22,"待制作")+COUNTIF('资产主表'!$K$6:$K$22,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$23,"待制作")+COUNTIF('资产主表'!$K$6:$K$23,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="33" t="n"/>
       <c r="G6" s="35">
-        <f>COUNTIF('资产主表'!$S$6:$S$22,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$23,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="33" t="n"/>
@@ -1152,11 +1152,11 @@
         </is>
       </c>
       <c r="B10" s="40">
-        <f>COUNTIF('资产主表'!$C$6:$C$22,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$23,A10)</f>
         <v/>
       </c>
       <c r="C10" s="40">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$22=A10)*(('资产主表'!$K$6:$K$22="已完成")+('资产主表'!$K$6:$K$22="原型已接入")+('资产主表'!$K$6:$K$22="正式美术已接入")+('资产主表'!$K$6:$K$22="已优化并正式接入")+('资产主表'!$K$6:$K$22="Blender源已完成")+('资产主表'!$K$6:$K$22="已导入；优化完成")+('资产主表'!$K$6:$K$22="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$23=A10)*(('资产主表'!$K$6:$K$23="已完成")+('资产主表'!$K$6:$K$23="原型已接入")+('资产主表'!$K$6:$K$23="正式美术已接入")+('资产主表'!$K$6:$K$23="已优化并正式接入")+('资产主表'!$K$6:$K$23="Blender源已完成")+('资产主表'!$K$6:$K$23="已导入；优化完成")+('资产主表'!$K$6:$K$23="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="40" t="n"/>
@@ -1174,11 +1174,11 @@
         </is>
       </c>
       <c r="B11" s="40">
-        <f>COUNTIF('资产主表'!$C$6:$C$22,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$23,A11)</f>
         <v/>
       </c>
       <c r="C11" s="40">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$22=A11)*(('资产主表'!$K$6:$K$22="已完成")+('资产主表'!$K$6:$K$22="原型已接入")+('资产主表'!$K$6:$K$22="正式美术已接入")+('资产主表'!$K$6:$K$22="已优化并正式接入")+('资产主表'!$K$6:$K$22="Blender源已完成")+('资产主表'!$K$6:$K$22="已导入；优化完成")+('资产主表'!$K$6:$K$22="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$23=A11)*(('资产主表'!$K$6:$K$23="已完成")+('资产主表'!$K$6:$K$23="原型已接入")+('资产主表'!$K$6:$K$23="正式美术已接入")+('资产主表'!$K$6:$K$23="已优化并正式接入")+('资产主表'!$K$6:$K$23="Blender源已完成")+('资产主表'!$K$6:$K$23="已导入；优化完成")+('资产主表'!$K$6:$K$23="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="40" t="n"/>
@@ -1941,7 +1941,7 @@
         <v/>
       </c>
       <c r="S6" s="51">
-        <f>IF(COUNTIF($R$6:$R$22,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="50" t="inlineStr">
@@ -2054,7 +2054,7 @@
         <v/>
       </c>
       <c r="S7" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="54" t="n"/>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="S8" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="54" t="n"/>
@@ -2268,7 +2268,7 @@
         <v/>
       </c>
       <c r="S9" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="54" t="n"/>
@@ -2375,7 +2375,7 @@
         <v/>
       </c>
       <c r="S10" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="54" t="n"/>
@@ -2482,7 +2482,7 @@
         <v/>
       </c>
       <c r="S11" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="54" t="n"/>
@@ -2589,7 +2589,7 @@
         <v/>
       </c>
       <c r="S12" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="54" t="n"/>
@@ -2704,7 +2704,7 @@
         <v/>
       </c>
       <c r="S13" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="54" t="inlineStr">
@@ -2815,7 +2815,7 @@
         <v/>
       </c>
       <c r="S14" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="54" t="n"/>
@@ -2922,7 +2922,7 @@
         <v/>
       </c>
       <c r="S15" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="54" t="n"/>
@@ -3029,7 +3029,7 @@
         <v/>
       </c>
       <c r="S16" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="54" t="n"/>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="S17" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="54" t="n"/>
@@ -3255,7 +3255,7 @@
         <v/>
       </c>
       <c r="S18" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="54" t="inlineStr">
@@ -3375,7 +3375,7 @@
         <v/>
       </c>
       <c r="S19" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="54" t="inlineStr">
@@ -3499,7 +3499,7 @@
         <v/>
       </c>
       <c r="S20" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="54" t="inlineStr">
@@ -3622,7 +3622,7 @@
         <v/>
       </c>
       <c r="S21" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="54" t="inlineStr">
@@ -3747,7 +3747,7 @@
         <v/>
       </c>
       <c r="S22" s="42">
-        <f>IF(COUNTIF($R$6:$R$22,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$23,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="54" t="inlineStr">
@@ -3779,32 +3779,129 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="30">
-      <c r="A23" s="54" t="n"/>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="42" t="n"/>
-      <c r="D23" s="54" t="n"/>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="54" t="n"/>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="54" t="n"/>
-      <c r="K23" s="42" t="n"/>
-      <c r="L23" s="54" t="n"/>
-      <c r="M23" s="54" t="n"/>
-      <c r="N23" s="54" t="n"/>
-      <c r="O23" s="54" t="n"/>
-      <c r="P23" s="54" t="n"/>
-      <c r="Q23" s="54" t="n"/>
-      <c r="R23" s="54" t="n"/>
-      <c r="S23" s="42" t="n"/>
-      <c r="T23" s="54" t="n"/>
-      <c r="U23" s="54" t="n"/>
-      <c r="V23" s="55" t="n"/>
-      <c r="W23" s="54" t="n"/>
-      <c r="X23" s="53" t="n"/>
-      <c r="Y23" s="54" t="n"/>
+    <row r="23" ht="126.85" customHeight="1" s="30">
+      <c r="A23" s="54" t="inlineStr">
+        <is>
+          <t>UI-PANEL-FATE-SOURCE</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>命运来源选择面板</t>
+        </is>
+      </c>
+      <c r="C23" s="54" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="E23" s="54" t="inlineStr">
+        <is>
+          <t>fate_source_select</t>
+        </is>
+      </c>
+      <c r="F23" s="54" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="G23" s="54" t="inlineStr">
+        <is>
+          <t>UI-SCREEN-FATE-SELECT</t>
+        </is>
+      </c>
+      <c r="H23" s="42" t="inlineStr">
+        <is>
+          <t>屏幕空间</t>
+        </is>
+      </c>
+      <c r="I23" s="54" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J23" s="42" t="inlineStr">
+        <is>
+          <t>命运卡三选一/占卜屋/工作台/待领命运</t>
+        </is>
+      </c>
+      <c r="K23" s="42" t="inlineStr">
+        <is>
+          <t>原型已接入</t>
+        </is>
+      </c>
+      <c r="L23" s="54" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M23" s="54" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N23" s="54" t="inlineStr">
+        <is>
+          <t>模态弹窗620×470；候选96×96 3D投影图标；卡片最小高108</t>
+        </is>
+      </c>
+      <c r="O23" s="54" t="inlineStr">
+        <is>
+          <t>src/ui/FateSourceSelectionPanel.gd</t>
+        </is>
+      </c>
+      <c r="P23" s="54" t="inlineStr">
+        <is>
+          <t>src/game/FateCardGameBridge.gd;docs/v0.1/14_技术施工_命运塔罗牌组.md</t>
+        </is>
+      </c>
+      <c r="Q23" s="54" t="inlineStr">
+        <is>
+          <t>命运来源;来源快照;枪械图标;3D投影;不消耗来源</t>
+        </is>
+      </c>
+      <c r="R23" s="54">
+        <f>LOWER(TRIM(C23)&amp;"|"&amp;TRIM(D23)&amp;"|"&amp;TRIM(E23)&amp;"|"&amp;TRIM(F23)&amp;"|"&amp;TRIM(H23)&amp;"|"&amp;TRIM(I23))</f>
+        <v/>
+      </c>
+      <c r="S23" s="42">
+        <f>IF(COUNTIF($R$6:$R$23,R23)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T23" s="54" t="inlineStr">
+        <is>
+          <t>b549c633dde04ccf99e8d921265e7279f6ba674763fb22c805b2d279871e3356</t>
+        </is>
+      </c>
+      <c r="U23" s="54" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V23" s="55" t="n">
+        <v>46305</v>
+      </c>
+      <c r="W23" s="42" t="inlineStr">
+        <is>
+          <t>原创程序UI</t>
+        </is>
+      </c>
+      <c r="X23" s="53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y23" s="42" t="inlineStr">
+        <is>
+          <t>2026-10-10：来源选择由纯文字按钮改为图标卡片 —— 左侧 ItemModelIcon3D 投影真实枪械模型（与地面拾取/背包/商人同源，含该枪此刻的装配与命运改装），右侧显示中文武器名、来源位置与命运槽占用；窗口标题不再重复进正文，正文改为一句只读语义说明。旧版单枪玩家会看到两个相同的 GunBody_* 名字，既认不出是哪把枪，也看不出该不该选、取消会不会吞卡。取消/Esc/关窗三路均保留卡片。同一面板亦服务「待领命运奖励」：该路径条目不带 icon_item，面板回退纯文字行，不新增第二个面板资产。
+2026-10-10 AST：登记路径 src/ui/FateSourceSelectionPanel.gd。</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="30">
       <c r="A24" s="54" t="n"/>
@@ -5307,7 +5404,7 @@
     <row r="427" ht="84.75" customHeight="1" s="30"/>
     <row r="429" ht="120" customHeight="1" s="30"/>
   </sheetData>
-  <autoFilter ref="A5:X22"/>
+  <autoFilter ref="A5:X23"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -5326,21 +5423,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="C23:C79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
-      <formula2>0</formula2>
+    <dataValidation sqref="K6:K23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,design_only,authored,exported_pending_godot_validation,validated,active,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
-      <formula2>0</formula2>
+    <dataValidation sqref="L6:L23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"P0,P1,P2,P3"</formula1>
-      <formula2>0</formula2>
+    <dataValidation sqref="C6:C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"UI"</formula1>
     </dataValidation>
-    <dataValidation sqref="C6:C22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"UI"</formula1>
-      <formula2>0</formula2>
+    <dataValidation sqref="C24:C79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音效,音乐"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -5358,7 +5451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="29" min="1" max="1"/>
@@ -5533,7 +5626,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" s="30">
       <c r="A9" s="40" t="inlineStr">
         <is>
           <t>v0.2.3</t>
@@ -5565,6 +5658,43 @@
         </is>
       </c>
       <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" s="30">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>v0.2.4</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>面板表现重做</t>
+        </is>
+      </c>
+      <c r="D10" s="40" t="inlineStr">
+        <is>
+          <t>UI-PANEL-FATE-SOURCE</t>
+        </is>
+      </c>
+      <c r="E10" s="41" t="inlineStr">
+        <is>
+          <t>命运来源选择面板由纯文字按钮改为图标卡片：左侧复用 UI-ICON-ITEM-MODEL-3D 投影真实枪械模型（与地面拾取/背包/商人同源），右侧显示中文武器名、来源位置与命运槽占用；标题不再重复正文，改为一句只读语义说明。同面板亦服务待领命运奖励（无 icon_item 时回退文字行）。</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>仅表现层；AssetID/存档/卡牌数值/来源事务与槽位规则不变。新增资产行 ⇒ 其余 17 行内容未变，仅《总览》区间随之扩到 $23（属预期）。无损基线已按既有「从当前分账本重建」口径做最小补录。</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
         <is>
           <t>Codex</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
@@ -2656,7 +2656,7 @@
       </c>
       <c r="I13" s="54" t="inlineStr">
         <is>
-          <t>主楼先起/双入口错峰/波浪扫描/方块粒子/倒序收起</t>
+          <t>主楼/楼群展开→最后阶段入口楼→动画结束标记与交互同步；02通关01后解锁</t>
         </is>
       </c>
       <c r="J13" s="42" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="N13" s="54" t="inlineStr">
         <is>
-          <t>主体约3.1m宽；42座外缘错落楼群；径向密度衰减；GPU逐块升降；2座楼顶入口</t>
+          <t>保持既有城市布局；锁定2座入口，解锁后01后方增加02大楼与入口</t>
         </is>
       </c>
       <c r="O13" s="54" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Q13" s="54" t="inlineStr">
         <is>
-          <t>远征情报室;全息城市;镜头拉近;远征01;测试99;3D选关</t>
+          <t>远征情报室;全息城市;远征01;测试99;远征02;解锁</t>
         </is>
       </c>
       <c r="R13" s="54">
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="V13" s="55" t="n">
-        <v>46294</v>
+        <v>46307</v>
       </c>
       <c r="W13" s="42" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="Y13" s="42" t="inlineStr">
         <is>
-          <t>2026-09-29：按用户参考制作Box城市；提前1秒展开，继承原环境至近景后渐暗；主楼优先/入口错峰/方块过渡；同场景世界空间入口。真实渲染/点击/键盘/手柄/返程通过，参考图像素级一致性未签署。</t>
+          <t>2026-10-12：入口楼最后20%展开，结束时标记与输入同步；01成功撤离原子解锁02，未解锁保持原布局；02实图待建，入口提示尚未开放。验收见 development/2026-10-12_hologram02.md。</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="29" min="1" max="1"/>
@@ -5700,6 +5700,43 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>v0.2.2</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>入口时序与解锁</t>
+        </is>
+      </c>
+      <c r="D11" s="40" t="inlineStr">
+        <is>
+          <t>UI-SCREEN-LEVEL-SELECT</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="inlineStr">
+        <is>
+          <t>最终阶段入口及远征02后方建筑</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>01成功撤离解锁；02关卡待建</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
@@ -21,8 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -380,7 +381,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -551,6 +552,9 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
       <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3232,7 +3236,7 @@
       </c>
       <c r="N18" s="42" t="inlineStr">
         <is>
-          <t>全屏Control/12+2槽/96×96投影</t>
+          <t>1280×720 / 1920×1080；双侧面板；6×4连续棋盘，扩容滚动；居中角色预览</t>
         </is>
       </c>
       <c r="O18" s="54" t="inlineStr">
@@ -3260,7 +3264,7 @@
       </c>
       <c r="T18" s="54" t="inlineStr">
         <is>
-          <t>bab8a57d3f4ad87eeb33f92a5bc409aa7b1e93ca981078fb02d77a8abaa2ba65</t>
+          <t>0545dd0da2bac471f96d7a76fb398e437fd07b3f8de403120a062c69626f29b4</t>
         </is>
       </c>
       <c r="U18" s="54" t="inlineStr">
@@ -3268,8 +3272,8 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V18" s="54" t="n">
-        <v>46264</v>
+      <c r="V18" s="59" t="n">
+        <v>46310</v>
       </c>
       <c r="W18" s="42" t="inlineStr">
         <is>
@@ -3284,7 +3288,8 @@
       <c r="Y18" s="42" t="inlineStr">
         <is>
           <t>复用背包根身份的3D子变体；I/Tab；打开时锁输入；道具共用 ItemModelFactory3D；实际 ItemSlot 信号完成换枪 ｜ 2026-08-07：左角色装备/右包裹网格；主副武器、背包装备、快捷物、物品与保险格统一正方形图标；深蓝黑+霓虹青+生命红语言。
-2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_3d_inventory_weapon_flow；SHA ccd8f7d7f3c9→e2c3f432a561。</t>
+2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_3d_inventory_weapon_flow；SHA ccd8f7d7f3c9→e2c3f432a561。
+2026-10-15：鸭科夫参考双侧布局；整件物品命中、原生拖放、R旋转/Esc取消、面积/件数、扩容滚动；专项 verify_inventory_experience_visual / verify_grid_inventory_layout。代码可编辑源位于稳定 src/ui 路径。全局账本门禁与旧装备回归见 docs/v0.1/development/2026-10-15_inventory_experience.md。</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3481,7 @@
       </c>
       <c r="N20" s="54" t="inlineStr">
         <is>
-          <t>96×96 SubViewport/UPDATE_ONCE</t>
+          <t>背包大物品/角色384px最长边投影；其余调用保持原分辨率；UPDATE_ONCE</t>
         </is>
       </c>
       <c r="O20" s="54" t="inlineStr">
@@ -3513,7 +3518,7 @@
         </is>
       </c>
       <c r="V20" s="55" t="n">
-        <v>46225</v>
+        <v>46310</v>
       </c>
       <c r="W20" s="42" t="inlineStr">
         <is>
@@ -3527,7 +3532,8 @@
       </c>
       <c r="Y20" s="42" t="inlineStr">
         <is>
-          <t>与地面拾取共用 ItemModelFactory3D；96×96 内部视口缩放至56px槽位；只渲染一次；验收图：assets/art/ui/inventory_3d/ui_inventory_item_model_preview_v001.png</t>
+          <t>与地面拾取共用 ItemModelFactory3D；96×96 内部视口缩放至56px槽位；只渲染一次；验收图：assets/art/ui/inventory_3d/ui_inventory_item_model_preview_v001.png
+2026-10-15：支持384px投影；取景排除不可见网格，角色全身正面相机；未改此行登记的tscn，既有tscn哈希漂移保持待核对，不回填。</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="29" min="1" max="1"/>
@@ -5737,6 +5743,28 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>inventory-experience-r2</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>UI-SCREEN-INVENTORY-3D / UI-ICON-ITEM-MODEL-3D</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>双侧装备棋盘交互与真实渲染专项；保留非本次哈希漂移</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
@@ -2789,7 +2789,7 @@
       </c>
       <c r="K14" s="42" t="inlineStr">
         <is>
-          <t>程序占位</t>
+          <t>原型已接入</t>
         </is>
       </c>
       <c r="L14" s="54" t="inlineStr">
@@ -2804,10 +2804,14 @@
       </c>
       <c r="N14" s="54" t="inlineStr">
         <is>
-          <t>1280×720 基准；九宫格/矢量优先</t>
-        </is>
-      </c>
-      <c r="O14" s="54" t="n"/>
+          <t>双侧八列跨格仓储、定点转移、旋转、整理与存档回滚</t>
+        </is>
+      </c>
+      <c r="O14" s="54" t="inlineStr">
+        <is>
+          <t>src/ui/VaultMenu.gd</t>
+        </is>
+      </c>
       <c r="P14" s="54" t="inlineStr">
         <is>
           <t>src/ui/VaultMenu.gd</t>
@@ -2822,14 +2826,20 @@
         <f>IF(COUNTIF($R$6:$R$23,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
-      <c r="T14" s="54" t="n"/>
+      <c r="T14" s="54" t="inlineStr">
+        <is>
+          <t>9a60275f29d535fb8d537fcfef84f97016968bc91a193759d08f20258464302e</t>
+        </is>
+      </c>
       <c r="U14" s="42" t="inlineStr">
         <is>
           <t>待分配</t>
         </is>
       </c>
-      <c r="V14" s="55" t="n">
-        <v>46224</v>
+      <c r="V14" s="55" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W14" s="42" t="inlineStr">
         <is>
@@ -2843,7 +2853,7 @@
       </c>
       <c r="Y14" s="42" t="inlineStr">
         <is>
-          <t>先建组件库，再做页面，避免每页重复画按钮/面板</t>
+          <t>verify_inventory_experience_visual / verify_grid_inventory_layout；真实渲染及隔离输入验收；Windows光标异常限制见 docs/v0.1/development/2026-10-15_inventory_storage_r3.md</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3246,7 @@
       </c>
       <c r="N18" s="42" t="inlineStr">
         <is>
-          <t>1280×720 / 1920×1080；双侧面板；6×4连续棋盘，扩容滚动；居中角色预览</t>
+          <t>8列50px背包、8×2保险柜、中央拖放丢弃、上下14px、统一快捷槽</t>
         </is>
       </c>
       <c r="O18" s="54" t="inlineStr">
@@ -3264,7 +3274,7 @@
       </c>
       <c r="T18" s="54" t="inlineStr">
         <is>
-          <t>0545dd0da2bac471f96d7a76fb398e437fd07b3f8de403120a062c69626f29b4</t>
+          <t>851ed9b41520cc01966ea416db1024f75d20fc49b6c0bf5bd7f045b23ce78be2</t>
         </is>
       </c>
       <c r="U18" s="54" t="inlineStr">
@@ -3272,8 +3282,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V18" s="59" t="n">
-        <v>46310</v>
+      <c r="V18" s="59" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W18" s="42" t="inlineStr">
         <is>
@@ -3287,9 +3299,7 @@
       </c>
       <c r="Y18" s="42" t="inlineStr">
         <is>
-          <t>复用背包根身份的3D子变体；I/Tab；打开时锁输入；道具共用 ItemModelFactory3D；实际 ItemSlot 信号完成换枪 ｜ 2026-08-07：左角色装备/右包裹网格；主副武器、背包装备、快捷物、物品与保险格统一正方形图标；深蓝黑+霓虹青+生命红语言。
-2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_3d_inventory_weapon_flow；SHA ccd8f7d7f3c9→e2c3f432a561。
-2026-10-15：鸭科夫参考双侧布局；整件物品命中、原生拖放、R旋转/Esc取消、面积/件数、扩容滚动；专项 verify_inventory_experience_visual / verify_grid_inventory_layout。代码可编辑源位于稳定 src/ui 路径。全局账本门禁与旧装备回归见 docs/v0.1/development/2026-10-15_inventory_experience.md。</t>
+          <t>verify_inventory_experience_visual / verify_grid_inventory_layout；真实渲染及隔离输入验收；Windows光标异常限制见 docs/v0.1/development/2026-10-15_inventory_storage_r3.md</t>
         </is>
       </c>
     </row>
@@ -3605,12 +3615,12 @@
       </c>
       <c r="N21" s="54" t="inlineStr">
         <is>
-          <t>1280×720自适应</t>
+          <t>双侧贩卖机：购买货架、背包/仓库棋盘切换、选中出售与枪械二次确认</t>
         </is>
       </c>
       <c r="O21" s="54" t="inlineStr">
         <is>
-          <t>scenes/BaseVendingMenu.tscn</t>
+          <t>src/ui/BaseVendingMenu.gd</t>
         </is>
       </c>
       <c r="P21" s="42" t="inlineStr">
@@ -3633,7 +3643,7 @@
       </c>
       <c r="T21" s="54" t="inlineStr">
         <is>
-          <t>064d8c1f92cfa6e1724bab0980520481cd8de44b384e498456e1d1be806a4c7d</t>
+          <t>7b402e70868cafe62e48ee47dc42ff5cf2ea59d396f4258ae8d5cea97780d56d</t>
         </is>
       </c>
       <c r="U21" s="54" t="inlineStr">
@@ -3641,8 +3651,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V21" s="54" t="n">
-        <v>46264</v>
+      <c r="V21" s="54" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="W21" s="42" t="inlineStr">
         <is>
@@ -3656,9 +3668,7 @@
       </c>
       <c r="Y21" s="42" t="inlineStr">
         <is>
-          <t>左右买卖双栏；复用ItemModelIcon3D；资源与容量常驻；Esc退出 ｜ 2026-08-07：购买/出售改为3列商品卡网格，正方形ItemModelIcon3D，与I键背包同源；统一主HUD配色和按钮状态。
-2026-08-30 AST-02：登记路径规范化 scenes/BaseVendingMenu.tscn; src/ui/BaseVendingMenu.gd → scenes/BaseVendingMenu.tscn；多实现/源码依据保留在P列。
-2026-08-30 AST-02：补齐单一生产路径SHA；验收：verify_base_shop_save_flow；SHA 064d8c1f92cf。</t>
+          <t>verify_inventory_experience_visual / verify_grid_inventory_layout；真实渲染及隔离输入验收；Windows光标异常限制见 docs/v0.1/development/2026-10-15_inventory_storage_r3.md</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="29" min="1" max="1"/>
@@ -5765,6 +5775,28 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>v0.1.3</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>八列背包、棋盘保险柜与基地仓储</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>UI-SCREEN-INVENTORY-3D / UI-SCREEN-VAULT / UI-SCREEN-BASE-VENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_UI账本_v001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="域变更日志" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$23</definedName>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="T6" s="50" t="inlineStr">
         <is>
-          <t>87bf0961b7cc4e440181adc14af71a230053139d69cbf82fa35b2aed3616932a</t>
+          <t>3e75c4bb7beefb09e56600ffc7944102a40b34ff38a3cb473aad2420638552c8</t>
         </is>
       </c>
       <c r="U6" s="51" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="T18" s="54" t="inlineStr">
         <is>
-          <t>851ed9b41520cc01966ea416db1024f75d20fc49b6c0bf5bd7f045b23ce78be2</t>
+          <t>0612bbdc95cbbc47da24c15788b1fe61b92a2f5763b002a230f09617d34afdfb</t>
         </is>
       </c>
       <c r="U18" s="54" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="T19" s="54" t="inlineStr">
         <is>
-          <t>1562501df74afdbe5d57847632cc1d52a1453da9b1d5a9f40eed41cec942a57b</t>
+          <t>765bb6aac7b288452943790f1192937f3e51986a43d098d4d2a2efa82b50e459</t>
         </is>
       </c>
       <c r="U19" s="54" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="T20" s="54" t="inlineStr">
         <is>
-          <t>97c10f3884107c1263f3de1f8bc1ce84bb568ecd80418b62bdb023c55cdab9fe</t>
+          <t>7d3deb95a52bbebca119606ce4189e501a812ed496b7c2f8f1e389ebeeb38d3c</t>
         </is>
       </c>
       <c r="U20" s="54" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="T23" s="54" t="inlineStr">
         <is>
-          <t>b549c633dde04ccf99e8d921265e7279f6ba674763fb22c805b2d279871e3356</t>
+          <t>447a0d55fddbca95ba10fad42393c7a767ff90fd2c13dfc16db836ca3745b2bd</t>
         </is>
       </c>
       <c r="U23" s="54" t="inlineStr">
